--- a/artfynd/A 58620-2025 artfynd.xlsx
+++ b/artfynd/A 58620-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851024</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58620-2025 artfynd.xlsx
+++ b/artfynd/A 58620-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851024</v>
       </c>
       <c r="B2" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58620-2025 artfynd.xlsx
+++ b/artfynd/A 58620-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851024</v>
       </c>
       <c r="B2" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58620-2025 artfynd.xlsx
+++ b/artfynd/A 58620-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851024</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58620-2025 artfynd.xlsx
+++ b/artfynd/A 58620-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851024</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58620-2025 artfynd.xlsx
+++ b/artfynd/A 58620-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851024</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
